--- a/test-files/финансы.xlsx
+++ b/test-files/финансы.xlsx
@@ -58,7 +58,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,14 +425,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,19 +459,24 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>дата приёма</t>
+          <t>дата найма</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>образование</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Лебедева Светлана Петровна</t>
+          <t>Смирнова Татьяна Николаевна</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Разработчик</t>
+          <t>UX-исследователь</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -479,136 +485,432 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>139174</v>
+        <v>210603</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02.04.2019</t>
+          <t>30.08.2023</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Бакалавр</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Новиков Илья Романович</t>
+          <t>Сидорова Ольга Дмитриевна</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Дизайнер</t>
+          <t>Руководитель отдела</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Финансы</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>168940</v>
+        <v>117945</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.01.2018</t>
+          <t>09.02.2021</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Бакалавр</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Козлов Артём Олегович</t>
+          <t>Кузнецова Екатерина Игоревна</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Тестировщик</t>
+          <t>Финансовый аналитик</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>183085</v>
+        <v>121432.04</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.03.2019</t>
+          <t>02.08.2021</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Высшее техническое</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Новиков Илья Романович</t>
+          <t>Смирнов Владимир Андреевич</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HR-специалист</t>
+          <t>Аналитик</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>209637</v>
+        <v>103488.22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.03.2020</t>
+          <t>17.09.2021</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Магистратура</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Смирнов Владимир Андреевич</t>
+          <t>Петров Пётр Петрович</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Тимлид</t>
+          <t>Старший аналитик</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Аналитика</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>191394</v>
+        <v>298004</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.12.2023</t>
+          <t>16.06.2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Высшее техническое</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Иванов Иван Иванович</t>
+          <t>Волков Антон Игоревич</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Специалист по продажам</t>
+          <t>Разработчик</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>159843</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15.02.2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Высшее экономическое</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Кузнецова Екатерина Игоревна</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Старший аналитик</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>134032.39</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15.07.2022</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Незаконченное высшее</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Сидорова Ольга Дмитриевна</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Руководитель отдела</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Финансы</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>178085</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>21.03.2018</t>
+      <c r="D9" t="n">
+        <v>287745</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30.04.2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Высшее техническое</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Козлова Юлия Романовна</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Тимлид</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>115039.08</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>06.02.2023</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Незаконченное высшее</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Иванова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>54845.82</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04.12.2021</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Высшее техническое</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Козлова Юлия Романовна</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>55095</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02.06.2019</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Высшее техническое</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Попова Елена Александровна</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Старший аналитик</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>93984</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>15.04.2019</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Высшее экономическое</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Новиков Илья Романович</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>288033</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>13.06.2022</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Высшее экономическое</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Сидоров Алексей Николаевич</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Бухгалтер</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>272899</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Бакалавр</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Петров Пётр Петрович</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Старший разработчик</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>211885.81</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Магистратура</t>
         </is>
       </c>
     </row>
